--- a/test/excel/win/parts/struct-held/delete-rows-1-2.xlsx
+++ b/test/excel/win/parts/struct-held/delete-rows-1-2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-struct-held-45796-1\out\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-struct-held-30311-1\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E1C9C91-AE6A-4E01-A233-87FEE9DED53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0643B2DE-6B69-43B2-B7A5-58ED266367D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
